--- a/branches/fix/go-publish-package-registry/StructureDefinition-mii-lm-symptom.xlsx
+++ b/branches/fix/go-publish-package-registry/StructureDefinition-mii-lm-symptom.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T06:45:39+00:00</t>
+    <t>2026-09-10T07:21:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/fix/go-publish-package-registry/StructureDefinition-mii-lm-symptom.xlsx
+++ b/branches/fix/go-publish-package-registry/StructureDefinition-mii-lm-symptom.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T07:21:31+00:00</t>
+    <t>2026-09-10T07:30:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/fix/go-publish-package-registry/StructureDefinition-mii-lm-symptom.xlsx
+++ b/branches/fix/go-publish-package-registry/StructureDefinition-mii-lm-symptom.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T07:30:26+00:00</t>
+    <t>2026-09-10T07:39:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
